--- a/docs/feasibility/Map_to_Geojson_Gantt.xlsx
+++ b/docs/feasibility/Map_to_Geojson_Gantt.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Desktop\Map_to_Geojson-Converter\docs\feasibility\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{626267C6-76E0-44C2-A62B-90B77B3BE113}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CE1D6AC-97B9-428E-8B9D-D0EE36F185DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="8880" xr2:uid="{9327F8D6-4F37-4E25-8083-20A17765DC2F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9327F8D6-4F37-4E25-8083-20A17765DC2F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -42,18 +42,12 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="53">
   <si>
-    <t>Map to .geojson</t>
-  </si>
-  <si>
     <t>Project Start: 6 October 2025</t>
   </si>
   <si>
     <t>Month</t>
   </si>
   <si>
-    <t>Gantt v1.0.0</t>
-  </si>
-  <si>
     <t>Week</t>
   </si>
   <si>
@@ -87,93 +81,27 @@
     <t>END</t>
   </si>
   <si>
-    <t>Progettazzione del prototipo</t>
-  </si>
-  <si>
-    <t>Studio di fattibilità</t>
-  </si>
-  <si>
     <t>F,M,L</t>
   </si>
   <si>
-    <t>Progettazione Gantt</t>
-  </si>
-  <si>
     <t>M,L</t>
   </si>
   <si>
-    <t>Studio svg e geojson</t>
-  </si>
-  <si>
     <t>F</t>
   </si>
   <si>
-    <t xml:space="preserve">  Studio dataset</t>
-  </si>
-  <si>
     <t>F,L</t>
   </si>
   <si>
-    <t>Prototipo svg to geojson-converter</t>
-  </si>
-  <si>
-    <t>Introduzione dell AI</t>
-  </si>
-  <si>
-    <t>Ricerca del dataset</t>
-  </si>
-  <si>
-    <t>Ricerca del modello pre-trained</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Implementazione del modello</t>
-  </si>
-  <si>
-    <t>fine-tuning del modello</t>
-  </si>
-  <si>
-    <t>UI</t>
-  </si>
-  <si>
-    <t>Progettazione figma</t>
-  </si>
-  <si>
     <t>M</t>
   </si>
   <si>
-    <t>Implementazione front-end</t>
-  </si>
-  <si>
-    <t>Test Finale</t>
-  </si>
-  <si>
-    <t>Test del modello</t>
-  </si>
-  <si>
-    <t>Test finale progetto + front-end</t>
-  </si>
-  <si>
-    <t>Rilascio della beta e test degli utenti</t>
-  </si>
-  <si>
     <t xml:space="preserve">Marketing </t>
   </si>
   <si>
-    <t>Studio del brand</t>
-  </si>
-  <si>
     <t>L</t>
   </si>
   <si>
-    <t xml:space="preserve">Progettazione dell'entrata in mercato </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Progettazione marketing </t>
-  </si>
-  <si>
-    <t>Componenti:</t>
-  </si>
-  <si>
     <t>Fabio Ferro</t>
   </si>
   <si>
@@ -199,6 +127,78 @@
   </si>
   <si>
     <t>Costo Risorse Esterne:</t>
+  </si>
+  <si>
+    <t>Gantt v3.0.0</t>
+  </si>
+  <si>
+    <t>Map to .geojson converter</t>
+  </si>
+  <si>
+    <t>Collaborators</t>
+  </si>
+  <si>
+    <t>Research &amp; Prototyping</t>
+  </si>
+  <si>
+    <t>Feasibility Study</t>
+  </si>
+  <si>
+    <t>Gantt Prototype</t>
+  </si>
+  <si>
+    <t>SVG &amp; GeoJSON study</t>
+  </si>
+  <si>
+    <t>Dataset Study</t>
+  </si>
+  <si>
+    <t>SVG to GeoJSON protype</t>
+  </si>
+  <si>
+    <t>Dataset Research</t>
+  </si>
+  <si>
+    <t>Computer Vision Development</t>
+  </si>
+  <si>
+    <t>Libraries Research</t>
+  </si>
+  <si>
+    <t>Initial Implementation</t>
+  </si>
+  <si>
+    <t>More Features</t>
+  </si>
+  <si>
+    <t>UI Development</t>
+  </si>
+  <si>
+    <t>Figma design</t>
+  </si>
+  <si>
+    <t>Front-end implementation</t>
+  </si>
+  <si>
+    <t>Testing &amp; Release</t>
+  </si>
+  <si>
+    <t>Testing</t>
+  </si>
+  <si>
+    <t>Testing + UI</t>
+  </si>
+  <si>
+    <t>Beta release and user testing</t>
+  </si>
+  <si>
+    <t>Brand study</t>
+  </si>
+  <si>
+    <t>Market entry planning</t>
+  </si>
+  <si>
+    <t>Marketing planning</t>
   </si>
 </sst>
 </file>
@@ -1081,18 +1081,18 @@
   <sheetData>
     <row r="2" spans="3:47" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C2" s="62" t="s">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D2" s="62"/>
       <c r="E2" s="3"/>
     </row>
     <row r="3" spans="3:47" x14ac:dyDescent="0.25">
       <c r="C3" s="60" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3" s="60"/>
       <c r="H3" s="15" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3" s="61" t="str">
         <f>TEXT(I5,"MMM")</f>
@@ -1159,10 +1159,10 @@
     </row>
     <row r="4" spans="3:47" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="H4" s="16" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I4" s="8">
         <v>1</v>
@@ -1272,10 +1272,10 @@
     </row>
     <row r="5" spans="3:47" x14ac:dyDescent="0.25">
       <c r="F5" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H5" s="17" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I5" s="11">
         <v>45936</v>
@@ -1383,30 +1383,30 @@
         <v>46174</v>
       </c>
       <c r="AS5" s="49" t="s">
+        <v>5</v>
+      </c>
+      <c r="AT5" s="53" t="s">
+        <v>6</v>
+      </c>
+      <c r="AU5" s="50" t="s">
         <v>7</v>
-      </c>
-      <c r="AT5" s="53" t="s">
-        <v>8</v>
-      </c>
-      <c r="AU5" s="50" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="6" spans="3:47" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C6" s="36" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="36" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="36" t="s">
+      <c r="F6" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="36" t="s">
+      <c r="G6" s="37" t="s">
         <v>12</v>
-      </c>
-      <c r="F6" s="37" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6" s="37" t="s">
-        <v>14</v>
       </c>
       <c r="H6" s="4"/>
       <c r="I6" s="5"/>
@@ -1450,7 +1450,7 @@
     </row>
     <row r="7" spans="3:47" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C7" s="34" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="D7" s="34"/>
       <c r="E7" s="28"/>
@@ -1498,10 +1498,10 @@
     </row>
     <row r="8" spans="3:47" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C8" s="33" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="D8" s="33" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E8" s="27">
         <v>1</v>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="9" spans="3:47" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C9" s="33" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="D9" s="33" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E9" s="27">
         <v>1</v>
@@ -1631,13 +1631,13 @@
     </row>
     <row r="10" spans="3:47" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C10" s="33" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="D10" s="33" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E10" s="27">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="F10" s="30">
         <v>45955</v>
@@ -1696,10 +1696,10 @@
     </row>
     <row r="11" spans="3:47" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C11" s="33" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="D11" s="33" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E11" s="27">
         <v>0.2</v>
@@ -1761,10 +1761,10 @@
     </row>
     <row r="12" spans="3:47" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C12" s="33" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="D12" s="33" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E12" s="27">
         <v>0</v>
@@ -1826,7 +1826,7 @@
     </row>
     <row r="13" spans="3:47" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C13" s="35" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="D13" s="35"/>
       <c r="E13" s="31"/>
@@ -1883,10 +1883,10 @@
     </row>
     <row r="14" spans="3:47" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C14" s="33" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="D14" s="33" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E14" s="27">
         <v>0.2</v>
@@ -1948,10 +1948,10 @@
     </row>
     <row r="15" spans="3:47" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C15" s="33" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="D15" s="33" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E15" s="27">
         <v>0.2</v>
@@ -2013,10 +2013,10 @@
     </row>
     <row r="16" spans="3:47" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C16" s="33" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="D16" s="33" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E16" s="27">
         <v>0</v>
@@ -2078,10 +2078,10 @@
     </row>
     <row r="17" spans="3:47" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C17" s="33" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="D17" s="33" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E17" s="27">
         <v>0</v>
@@ -2143,7 +2143,7 @@
     </row>
     <row r="18" spans="3:47" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C18" s="35" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="D18" s="35"/>
       <c r="E18" s="31"/>
@@ -2200,10 +2200,10 @@
     </row>
     <row r="19" spans="3:47" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C19" s="33" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="D19" s="33" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="E19" s="27">
         <v>0</v>
@@ -2265,10 +2265,10 @@
     </row>
     <row r="20" spans="3:47" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C20" s="33" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D20" s="33" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="E20" s="27">
         <v>0</v>
@@ -2330,7 +2330,7 @@
     </row>
     <row r="21" spans="3:47" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C21" s="35" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D21" s="35"/>
       <c r="E21" s="31"/>
@@ -2387,10 +2387,10 @@
     </row>
     <row r="22" spans="3:47" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C22" s="33" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="D22" s="33" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E22" s="27">
         <v>0</v>
@@ -2452,10 +2452,10 @@
     </row>
     <row r="23" spans="3:47" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C23" s="33" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="D23" s="33" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E23" s="27">
         <v>0</v>
@@ -2517,7 +2517,7 @@
     </row>
     <row r="24" spans="3:47" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C24" s="33" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="D24" s="33"/>
       <c r="E24" s="26"/>
@@ -2578,7 +2578,7 @@
     </row>
     <row r="25" spans="3:47" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C25" s="35" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="D25" s="35"/>
       <c r="E25" s="31"/>
@@ -2635,13 +2635,13 @@
     </row>
     <row r="26" spans="3:47" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C26" s="33" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="D26" s="33" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="E26" s="27">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="F26" s="30">
         <v>45969</v>
@@ -2700,10 +2700,10 @@
     </row>
     <row r="27" spans="3:47" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C27" s="33" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="D27" s="33" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="E27" s="27">
         <v>0</v>
@@ -2765,10 +2765,10 @@
     </row>
     <row r="28" spans="3:47" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C28" s="33" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="D28" s="33" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="E28" s="27">
         <v>0</v>
@@ -2849,10 +2849,10 @@
     </row>
     <row r="32" spans="3:47" ht="18.600000000000001" x14ac:dyDescent="0.3">
       <c r="C32" s="46" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="D32" s="58" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="E32" s="58"/>
       <c r="F32" s="59"/>
@@ -2872,7 +2872,7 @@
     <row r="33" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C33" s="43"/>
       <c r="D33" s="58" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="E33" s="58"/>
       <c r="F33" s="59"/>
@@ -2880,7 +2880,7 @@
     <row r="34" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C34" s="43"/>
       <c r="D34" s="58" t="s">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="E34" s="58"/>
       <c r="F34" s="59"/>
@@ -2891,7 +2891,7 @@
     <row r="35" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C35" s="43"/>
       <c r="D35" s="58" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="E35" s="58"/>
       <c r="F35" s="59"/>
@@ -2919,13 +2919,13 @@
     </row>
     <row r="38" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C38" s="51" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="D38" s="47">
         <v>3</v>
       </c>
       <c r="E38" s="38" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="F38" s="42"/>
       <c r="J38" s="2"/>
@@ -2934,13 +2934,13 @@
     </row>
     <row r="39" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C39" s="51" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="D39" s="47">
         <v>15</v>
       </c>
       <c r="E39" s="38" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="F39" s="42"/>
       <c r="J39" s="2"/>
@@ -2949,13 +2949,13 @@
     </row>
     <row r="40" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C40" s="51" t="s">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="D40">
         <v>25</v>
       </c>
       <c r="E40" s="38" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="F40" s="48"/>
     </row>

--- a/docs/feasibility/Map_to_Geojson_Gantt.xlsx
+++ b/docs/feasibility/Map_to_Geojson_Gantt.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25225"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Desktop\Map_to_Geojson-Converter\docs\feasibility\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucac\Desktop\Map_to_Geojson-Converter\docs\feasibility\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CE1D6AC-97B9-428E-8B9D-D0EE36F185DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92FF8E1F-94EC-44D1-BA11-09B2218AA1B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9327F8D6-4F37-4E25-8083-20A17765DC2F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{9327F8D6-4F37-4E25-8083-20A17765DC2F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -670,6 +670,12 @@
     <xf numFmtId="166" fontId="0" fillId="12" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -678,12 +684,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1065,99 +1065,99 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{490757F6-93EC-4607-8435-BB8805CD3E41}">
   <dimension ref="C2:AU41"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="2.296875" customWidth="1"/>
+    <col min="1" max="1" width="2.26953125" customWidth="1"/>
     <col min="2" max="2" width="6" customWidth="1"/>
     <col min="3" max="3" width="23" customWidth="1"/>
-    <col min="4" max="4" width="13.09765625" customWidth="1"/>
-    <col min="5" max="5" width="9.3984375" customWidth="1"/>
-    <col min="6" max="6" width="10.296875" customWidth="1"/>
-    <col min="7" max="7" width="10.59765625" customWidth="1"/>
-    <col min="9" max="9" width="5.59765625" style="1" customWidth="1"/>
-    <col min="10" max="43" width="6.69921875" style="1" customWidth="1"/>
-    <col min="45" max="49" width="13.69921875" customWidth="1"/>
+    <col min="4" max="4" width="13.08984375" customWidth="1"/>
+    <col min="5" max="5" width="9.36328125" customWidth="1"/>
+    <col min="6" max="6" width="10.26953125" customWidth="1"/>
+    <col min="7" max="7" width="10.6328125" customWidth="1"/>
+    <col min="9" max="9" width="5.6328125" style="1" customWidth="1"/>
+    <col min="10" max="43" width="6.7265625" style="1" customWidth="1"/>
+    <col min="45" max="49" width="13.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:47" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C2" s="62" t="s">
+    <row r="2" spans="3:47" ht="27" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C2" s="59" t="s">
         <v>30</v>
       </c>
-      <c r="D2" s="62"/>
+      <c r="D2" s="59"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="3:47" x14ac:dyDescent="0.25">
-      <c r="C3" s="60" t="s">
+    <row r="3" spans="3:47" x14ac:dyDescent="0.35">
+      <c r="C3" s="62" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="60"/>
+      <c r="D3" s="62"/>
       <c r="H3" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="I3" s="61" t="str">
+      <c r="I3" s="58" t="str">
         <f>TEXT(I5,"MMM")</f>
         <v>ott</v>
       </c>
-      <c r="J3" s="61"/>
-      <c r="K3" s="61"/>
-      <c r="L3" s="61"/>
-      <c r="M3" s="61" t="str">
+      <c r="J3" s="58"/>
+      <c r="K3" s="58"/>
+      <c r="L3" s="58"/>
+      <c r="M3" s="58" t="str">
         <f>TEXT(M5,"MMM")</f>
         <v>nov</v>
       </c>
-      <c r="N3" s="61"/>
-      <c r="O3" s="61"/>
-      <c r="P3" s="61"/>
-      <c r="Q3" s="61" t="str">
+      <c r="N3" s="58"/>
+      <c r="O3" s="58"/>
+      <c r="P3" s="58"/>
+      <c r="Q3" s="58" t="str">
         <f>TEXT(Q5,"MMM")</f>
         <v>dic</v>
       </c>
-      <c r="R3" s="61"/>
-      <c r="S3" s="61"/>
-      <c r="T3" s="61"/>
+      <c r="R3" s="58"/>
+      <c r="S3" s="58"/>
+      <c r="T3" s="58"/>
       <c r="U3" s="7"/>
-      <c r="V3" s="61" t="str">
+      <c r="V3" s="58" t="str">
         <f>TEXT(V5,"MMM")</f>
         <v>gen</v>
       </c>
-      <c r="W3" s="61"/>
-      <c r="X3" s="61"/>
-      <c r="Y3" s="61"/>
-      <c r="Z3" s="61" t="str">
+      <c r="W3" s="58"/>
+      <c r="X3" s="58"/>
+      <c r="Y3" s="58"/>
+      <c r="Z3" s="58" t="str">
         <f>TEXT(Z5,"MMM")</f>
         <v>feb</v>
       </c>
-      <c r="AA3" s="61"/>
-      <c r="AB3" s="61"/>
-      <c r="AC3" s="61"/>
-      <c r="AD3" s="61" t="str">
+      <c r="AA3" s="58"/>
+      <c r="AB3" s="58"/>
+      <c r="AC3" s="58"/>
+      <c r="AD3" s="58" t="str">
         <f>TEXT(AD5,"MMM")</f>
         <v>mar</v>
       </c>
-      <c r="AE3" s="61"/>
-      <c r="AF3" s="61"/>
-      <c r="AG3" s="61"/>
+      <c r="AE3" s="58"/>
+      <c r="AF3" s="58"/>
+      <c r="AG3" s="58"/>
       <c r="AH3" s="7"/>
-      <c r="AI3" s="61" t="str">
+      <c r="AI3" s="58" t="str">
         <f>TEXT(AI5,"MMM")</f>
         <v>apr</v>
       </c>
-      <c r="AJ3" s="61"/>
-      <c r="AK3" s="61"/>
-      <c r="AL3" s="61"/>
-      <c r="AM3" s="61" t="str">
+      <c r="AJ3" s="58"/>
+      <c r="AK3" s="58"/>
+      <c r="AL3" s="58"/>
+      <c r="AM3" s="58" t="str">
         <f>TEXT(AM5,"MMM")</f>
         <v>mag</v>
       </c>
-      <c r="AN3" s="61"/>
-      <c r="AO3" s="61"/>
-      <c r="AP3" s="61"/>
+      <c r="AN3" s="58"/>
+      <c r="AO3" s="58"/>
+      <c r="AP3" s="58"/>
       <c r="AQ3" s="6" t="str">
         <f>TEXT(AQ5,"MMM")</f>
         <v>giu</v>
       </c>
     </row>
-    <row r="4" spans="3:47" x14ac:dyDescent="0.25">
+    <row r="4" spans="3:47" x14ac:dyDescent="0.35">
       <c r="C4" t="s">
         <v>29</v>
       </c>
@@ -1270,7 +1270,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="3:47" x14ac:dyDescent="0.25">
+    <row r="5" spans="3:47" x14ac:dyDescent="0.35">
       <c r="F5" t="s">
         <v>3</v>
       </c>
@@ -1392,7 +1392,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="3:47" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="3:47" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C6" s="36" t="s">
         <v>8</v>
       </c>
@@ -1448,7 +1448,7 @@
       <c r="AT6" s="54"/>
       <c r="AU6" s="56"/>
     </row>
-    <row r="7" spans="3:47" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="3:47" ht="25.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C7" s="34" t="s">
         <v>32</v>
       </c>
@@ -1496,7 +1496,7 @@
       <c r="AT7" s="54"/>
       <c r="AU7" s="56"/>
     </row>
-    <row r="8" spans="3:47" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="3:47" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C8" s="33" t="s">
         <v>33</v>
       </c>
@@ -1564,7 +1564,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="9" spans="3:47" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="3:47" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C9" s="33" t="s">
         <v>34</v>
       </c>
@@ -1629,7 +1629,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="10" spans="3:47" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="3:47" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C10" s="33" t="s">
         <v>35</v>
       </c>
@@ -1637,7 +1637,7 @@
         <v>15</v>
       </c>
       <c r="E10" s="27">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="F10" s="30">
         <v>45955</v>
@@ -1694,7 +1694,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="11" spans="3:47" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="3:47" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C11" s="33" t="s">
         <v>36</v>
       </c>
@@ -1702,7 +1702,7 @@
         <v>16</v>
       </c>
       <c r="E11" s="27">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="F11" s="30">
         <v>45969</v>
@@ -1759,7 +1759,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="12" spans="3:47" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="3:47" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C12" s="33" t="s">
         <v>37</v>
       </c>
@@ -1767,7 +1767,7 @@
         <v>13</v>
       </c>
       <c r="E12" s="27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" s="30">
         <v>45976</v>
@@ -1824,7 +1824,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="13" spans="3:47" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="3:47" ht="25.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C13" s="35" t="s">
         <v>39</v>
       </c>
@@ -1881,7 +1881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="3:47" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="3:47" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C14" s="33" t="s">
         <v>38</v>
       </c>
@@ -1889,7 +1889,7 @@
         <v>16</v>
       </c>
       <c r="E14" s="27">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="F14" s="30">
         <v>45969</v>
@@ -1946,7 +1946,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="15" spans="3:47" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="3:47" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C15" s="33" t="s">
         <v>40</v>
       </c>
@@ -1954,7 +1954,7 @@
         <v>15</v>
       </c>
       <c r="E15" s="27">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="F15" s="30">
         <v>45969</v>
@@ -2011,7 +2011,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="16" spans="3:47" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="3:47" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C16" s="33" t="s">
         <v>41</v>
       </c>
@@ -2019,7 +2019,7 @@
         <v>15</v>
       </c>
       <c r="E16" s="27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" s="30">
         <v>45990</v>
@@ -2076,7 +2076,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="17" spans="3:47" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="3:47" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C17" s="33" t="s">
         <v>42</v>
       </c>
@@ -2084,7 +2084,7 @@
         <v>15</v>
       </c>
       <c r="E17" s="27">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="F17" s="30">
         <v>45997</v>
@@ -2141,7 +2141,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="18" spans="3:47" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="3:47" ht="25.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C18" s="35" t="s">
         <v>43</v>
       </c>
@@ -2198,7 +2198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="3:47" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="3:47" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C19" s="33" t="s">
         <v>44</v>
       </c>
@@ -2206,7 +2206,7 @@
         <v>17</v>
       </c>
       <c r="E19" s="27">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="F19" s="30">
         <v>46067</v>
@@ -2263,7 +2263,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="20" spans="3:47" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="3:47" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C20" s="33" t="s">
         <v>45</v>
       </c>
@@ -2328,7 +2328,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="21" spans="3:47" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="3:47" ht="25.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C21" s="35" t="s">
         <v>46</v>
       </c>
@@ -2385,7 +2385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="3:47" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="3:47" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C22" s="33" t="s">
         <v>47</v>
       </c>
@@ -2393,7 +2393,7 @@
         <v>13</v>
       </c>
       <c r="E22" s="27">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="F22" s="30">
         <v>45976</v>
@@ -2450,7 +2450,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="23" spans="3:47" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="3:47" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C23" s="33" t="s">
         <v>48</v>
       </c>
@@ -2515,12 +2515,14 @@
         <v>180</v>
       </c>
     </row>
-    <row r="24" spans="3:47" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="3:47" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C24" s="33" t="s">
         <v>49</v>
       </c>
       <c r="D24" s="33"/>
-      <c r="E24" s="26"/>
+      <c r="E24" s="27">
+        <v>0</v>
+      </c>
       <c r="F24" s="30">
         <v>46085</v>
       </c>
@@ -2576,7 +2578,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="25" spans="3:47" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="3:47" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C25" s="35" t="s">
         <v>18</v>
       </c>
@@ -2633,7 +2635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="3:47" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="3:47" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C26" s="33" t="s">
         <v>50</v>
       </c>
@@ -2641,7 +2643,7 @@
         <v>19</v>
       </c>
       <c r="E26" s="27">
-        <v>0.15</v>
+        <v>0.45</v>
       </c>
       <c r="F26" s="30">
         <v>45969</v>
@@ -2698,7 +2700,7 @@
         <v>1305</v>
       </c>
     </row>
-    <row r="27" spans="3:47" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="3:47" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C27" s="33" t="s">
         <v>51</v>
       </c>
@@ -2763,7 +2765,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="28" spans="3:47" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="3:47" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C28" s="33" t="s">
         <v>52</v>
       </c>
@@ -2771,7 +2773,7 @@
         <v>19</v>
       </c>
       <c r="E28" s="27">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="F28" s="30">
         <v>45962</v>
@@ -2828,17 +2830,17 @@
         <v>1350</v>
       </c>
     </row>
-    <row r="29" spans="3:47" x14ac:dyDescent="0.25">
+    <row r="29" spans="3:47" x14ac:dyDescent="0.35">
       <c r="AS29" s="8"/>
       <c r="AT29" s="54"/>
       <c r="AU29" s="56"/>
     </row>
-    <row r="30" spans="3:47" x14ac:dyDescent="0.25">
+    <row r="30" spans="3:47" x14ac:dyDescent="0.35">
       <c r="AS30" s="8"/>
       <c r="AT30" s="54"/>
       <c r="AU30" s="56"/>
     </row>
-    <row r="31" spans="3:47" x14ac:dyDescent="0.25">
+    <row r="31" spans="3:47" x14ac:dyDescent="0.35">
       <c r="C31" s="39"/>
       <c r="D31" s="40"/>
       <c r="E31" s="40"/>
@@ -2847,15 +2849,15 @@
       <c r="AT31" s="54"/>
       <c r="AU31" s="56"/>
     </row>
-    <row r="32" spans="3:47" ht="18.600000000000001" x14ac:dyDescent="0.3">
+    <row r="32" spans="3:47" ht="19.5" x14ac:dyDescent="0.45">
       <c r="C32" s="46" t="s">
         <v>31</v>
       </c>
-      <c r="D32" s="58" t="s">
+      <c r="D32" s="60" t="s">
         <v>20</v>
       </c>
-      <c r="E32" s="58"/>
-      <c r="F32" s="59"/>
+      <c r="E32" s="60"/>
+      <c r="F32" s="61"/>
       <c r="AS32" s="52">
         <f>SUM(AS8:AS24)</f>
         <v>67</v>
@@ -2869,37 +2871,37 @@
         <v>3015</v>
       </c>
     </row>
-    <row r="33" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="3:12" x14ac:dyDescent="0.35">
       <c r="C33" s="43"/>
-      <c r="D33" s="58" t="s">
+      <c r="D33" s="60" t="s">
         <v>21</v>
       </c>
-      <c r="E33" s="58"/>
-      <c r="F33" s="59"/>
-    </row>
-    <row r="34" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="E33" s="60"/>
+      <c r="F33" s="61"/>
+    </row>
+    <row r="34" spans="3:12" x14ac:dyDescent="0.35">
       <c r="C34" s="43"/>
-      <c r="D34" s="58" t="s">
+      <c r="D34" s="60" t="s">
         <v>22</v>
       </c>
-      <c r="E34" s="58"/>
-      <c r="F34" s="59"/>
+      <c r="E34" s="60"/>
+      <c r="F34" s="61"/>
       <c r="J34" s="2"/>
       <c r="K34" s="2"/>
       <c r="L34" s="2"/>
     </row>
-    <row r="35" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="3:12" x14ac:dyDescent="0.35">
       <c r="C35" s="43"/>
-      <c r="D35" s="58" t="s">
+      <c r="D35" s="60" t="s">
         <v>23</v>
       </c>
-      <c r="E35" s="58"/>
-      <c r="F35" s="59"/>
+      <c r="E35" s="60"/>
+      <c r="F35" s="61"/>
       <c r="J35" s="2"/>
       <c r="K35" s="2"/>
       <c r="L35" s="2"/>
     </row>
-    <row r="36" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="3:12" x14ac:dyDescent="0.35">
       <c r="C36" s="43"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
@@ -2908,7 +2910,7 @@
       <c r="K36" s="2"/>
       <c r="L36" s="2"/>
     </row>
-    <row r="37" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="3:12" x14ac:dyDescent="0.35">
       <c r="C37" s="43"/>
       <c r="D37" s="1"/>
       <c r="E37" s="1"/>
@@ -2917,7 +2919,7 @@
       <c r="K37" s="2"/>
       <c r="L37" s="2"/>
     </row>
-    <row r="38" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="3:12" x14ac:dyDescent="0.35">
       <c r="C38" s="51" t="s">
         <v>24</v>
       </c>
@@ -2932,7 +2934,7 @@
       <c r="K38" s="2"/>
       <c r="L38" s="2"/>
     </row>
-    <row r="39" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="3:12" x14ac:dyDescent="0.35">
       <c r="C39" s="51" t="s">
         <v>26</v>
       </c>
@@ -2947,7 +2949,7 @@
       <c r="K39" s="2"/>
       <c r="L39" s="2"/>
     </row>
-    <row r="40" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="3:12" x14ac:dyDescent="0.35">
       <c r="C40" s="51" t="s">
         <v>28</v>
       </c>
@@ -2959,7 +2961,7 @@
       </c>
       <c r="F40" s="48"/>
     </row>
-    <row r="41" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="3:12" x14ac:dyDescent="0.35">
       <c r="C41" s="44"/>
       <c r="D41" s="21"/>
       <c r="E41" s="21"/>
@@ -2967,6 +2969,11 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="D34:F34"/>
+    <mergeCell ref="D35:F35"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="V3:Y3"/>
     <mergeCell ref="Z3:AC3"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="D32:F32"/>
@@ -2976,11 +2983,6 @@
     <mergeCell ref="M3:P3"/>
     <mergeCell ref="Q3:T3"/>
     <mergeCell ref="AD3:AG3"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="D34:F34"/>
-    <mergeCell ref="D35:F35"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="V3:Y3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="E8:E28">
@@ -2997,12 +2999,12 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H8:AP8 I9:AP11 I5:AQ7 AQ8:AQ11 I12:AQ28">
+  <conditionalFormatting sqref="H8:AP8 I9:AP11 I12:AQ28 I5:AQ7 AQ8:AQ11">
     <cfRule type="expression" dxfId="2" priority="13">
       <formula>AND(H$5&lt;=TODAY(), (I$5-7)&lt;=TODAY(),I$5&gt;=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H8:AP8 I9:AP12 I14:V28 Y14:AD28 AG14:AL28 AO14:AP28 W16:X28 AE17:AF28 AM16:AN28">
+  <conditionalFormatting sqref="H8:AP8 I9:AP12 I14:V28 Y14:AD28 AG14:AL28 AO14:AP28 W16:X28 AM16:AN28 AE17:AF28">
     <cfRule type="expression" dxfId="1" priority="10">
       <formula>AND(H$5&gt;=$F8,H$5&lt;=$G8)</formula>
     </cfRule>
@@ -3048,15 +3050,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101000CB21FEEF28D25478970655B8FB038CE" ma:contentTypeVersion="15" ma:contentTypeDescription="Creare un nuovo documento." ma:contentTypeScope="" ma:versionID="902da41986bab8a11f80b3f30157db2f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="86ef1eb3-aa3a-41d9-a687-33c02a66b6e6" xmlns:ns4="21196a8f-ca16-4a74-9c8b-eedfa456e3d4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b98c4e8fb50649dd042a3053bc038173" ns3:_="" ns4:_="">
     <xsd:import namespace="86ef1eb3-aa3a-41d9-a687-33c02a66b6e6"/>
@@ -3289,6 +3282,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E9D20626-14A6-4435-970B-5FFE0A067F50}">
   <ds:schemaRefs>
@@ -3300,14 +3302,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A350BD29-387B-4299-94F6-FB37861A0D12}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1782BAEA-5410-40EE-BD4C-7C24CB75978C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3324,4 +3318,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A350BD29-387B-4299-94F6-FB37861A0D12}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>